--- a/diseases/d124/1985-1989.xlsx
+++ b/diseases/d124/1985-1989.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22068,7 +22068,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">

--- a/diseases/d124/1985-1989.xlsx
+++ b/diseases/d124/1985-1989.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22068,7 +22068,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
